--- a/data/nzd0583/nzd0583.xlsx
+++ b/data/nzd0583/nzd0583.xlsx
@@ -9848,9 +9848,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0286</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -9898,9 +9904,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0306</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -9948,9 +9960,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0356</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -9998,9 +10016,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -10048,9 +10072,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -10098,9 +10128,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -10148,9 +10184,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -10198,9 +10240,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -10248,9 +10296,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -10298,9 +10352,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -10348,9 +10408,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>

--- a/data/nzd0583/nzd0583.xlsx
+++ b/data/nzd0583/nzd0583.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12114,7 +12114,7 @@
         <v>217.73</v>
       </c>
       <c r="H263" t="n">
-        <v>233.97</v>
+        <v>246.16</v>
       </c>
       <c r="I263" t="n">
         <v>245.03</v>
@@ -12131,6 +12131,51 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:27+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>192.08</v>
+      </c>
+      <c r="C264" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="D264" t="n">
+        <v>190.14</v>
+      </c>
+      <c r="E264" t="n">
+        <v>218.94</v>
+      </c>
+      <c r="F264" t="n">
+        <v>215.26</v>
+      </c>
+      <c r="G264" t="n">
+        <v>217.73</v>
+      </c>
+      <c r="H264" t="n">
+        <v>246.16</v>
+      </c>
+      <c r="I264" t="n">
+        <v>247.71</v>
+      </c>
+      <c r="J264" t="n">
+        <v>233.65</v>
+      </c>
+      <c r="K264" t="n">
+        <v>235.87</v>
+      </c>
+      <c r="L264" t="n">
+        <v>253.1</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14938,6 +14983,16 @@
       </c>
       <c r="B279" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -15100,28 +15155,28 @@
         <v>0.0286</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1690854924936196</v>
+        <v>-0.1910780270716345</v>
       </c>
       <c r="J2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002635989772187819</v>
+        <v>0.003373336088892009</v>
       </c>
       <c r="M2" t="n">
-        <v>18.56881577646773</v>
+        <v>18.61388512281568</v>
       </c>
       <c r="N2" t="n">
-        <v>565.2906506350134</v>
+        <v>566.0646839709801</v>
       </c>
       <c r="O2" t="n">
-        <v>23.77584174398487</v>
+        <v>23.7921139029507</v>
       </c>
       <c r="P2" t="n">
-        <v>224.2189971278531</v>
+        <v>224.4618249062655</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15172,28 +15227,28 @@
         <v>0.0306</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.252205994271629</v>
+        <v>-4.250926362903943</v>
       </c>
       <c r="J3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.266538200154068</v>
+        <v>0.2680276683089654</v>
       </c>
       <c r="M3" t="n">
-        <v>38.2239911660794</v>
+        <v>38.06413567695475</v>
       </c>
       <c r="N3" t="n">
-        <v>2536.350038227011</v>
+        <v>2525.521098821678</v>
       </c>
       <c r="O3" t="n">
-        <v>50.36218857661977</v>
+        <v>50.25456296518435</v>
       </c>
       <c r="P3" t="n">
-        <v>308.1574287658227</v>
+        <v>308.1428673961782</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15244,28 +15299,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.685884060213656</v>
+        <v>-1.698613334328617</v>
       </c>
       <c r="J4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0944989131676427</v>
+        <v>0.09642560685179069</v>
       </c>
       <c r="M4" t="n">
-        <v>23.54565359675339</v>
+        <v>23.55103389065146</v>
       </c>
       <c r="N4" t="n">
-        <v>1555.938525757887</v>
+        <v>1550.919292400599</v>
       </c>
       <c r="O4" t="n">
-        <v>39.44538662198518</v>
+        <v>39.38171266464422</v>
       </c>
       <c r="P4" t="n">
-        <v>251.8698606089687</v>
+        <v>252.001805409406</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15316,28 +15371,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3426218326881142</v>
+        <v>-0.3364754107873615</v>
       </c>
       <c r="J5" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K5" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0490452798872778</v>
+        <v>0.04765760147001519</v>
       </c>
       <c r="M5" t="n">
-        <v>9.342910469566934</v>
+        <v>9.337520200195</v>
       </c>
       <c r="N5" t="n">
-        <v>126.7570277223624</v>
+        <v>126.5311680310557</v>
       </c>
       <c r="O5" t="n">
-        <v>11.25864235697903</v>
+        <v>11.24860738185202</v>
       </c>
       <c r="P5" t="n">
-        <v>219.7164447553354</v>
+        <v>219.6522633173945</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15388,28 +15443,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.004464725525919991</v>
+        <v>-0.00205527658875659</v>
       </c>
       <c r="J6" t="n">
+        <v>263</v>
+      </c>
+      <c r="K6" t="n">
         <v>262</v>
       </c>
-      <c r="K6" t="n">
-        <v>261</v>
-      </c>
       <c r="L6" t="n">
-        <v>3.916653357527444e-05</v>
+        <v>8.355507083335212e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87585332948143</v>
+        <v>3.87453531233782</v>
       </c>
       <c r="N6" t="n">
-        <v>28.5723431152292</v>
+        <v>28.5036411708857</v>
       </c>
       <c r="O6" t="n">
-        <v>5.345310385303102</v>
+        <v>5.338880142022829</v>
       </c>
       <c r="P6" t="n">
-        <v>212.1050957826317</v>
+        <v>212.0801005028477</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15460,28 +15515,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3195687659748876</v>
+        <v>-0.3174912490368344</v>
       </c>
       <c r="J7" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K7" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1164614987722561</v>
+        <v>0.1158775392752188</v>
       </c>
       <c r="M7" t="n">
-        <v>5.06783247562851</v>
+        <v>5.05669255644027</v>
       </c>
       <c r="N7" t="n">
-        <v>44.03877336972995</v>
+        <v>43.89855535203931</v>
       </c>
       <c r="O7" t="n">
-        <v>6.636171589834755</v>
+        <v>6.625598490101805</v>
       </c>
       <c r="P7" t="n">
-        <v>223.3575372461889</v>
+        <v>223.3360804425485</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15532,28 +15587,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7909121028297048</v>
+        <v>-0.7644456403292758</v>
       </c>
       <c r="J8" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K8" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2210074831620298</v>
+        <v>0.2058767093551377</v>
       </c>
       <c r="M8" t="n">
-        <v>8.918461665111209</v>
+        <v>9.04161123434522</v>
       </c>
       <c r="N8" t="n">
-        <v>125.7802748482954</v>
+        <v>129.1258984947875</v>
       </c>
       <c r="O8" t="n">
-        <v>11.2151805535308</v>
+        <v>11.36335771217238</v>
       </c>
       <c r="P8" t="n">
-        <v>243.1856896499947</v>
+        <v>242.9136212852171</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15604,28 +15659,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7498218595446153</v>
+        <v>-0.742583485839218</v>
       </c>
       <c r="J9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2979141509638095</v>
+        <v>0.2945272653957833</v>
       </c>
       <c r="M9" t="n">
-        <v>6.219783580516913</v>
+        <v>6.231701469502525</v>
       </c>
       <c r="N9" t="n">
-        <v>74.60308538390024</v>
+        <v>74.68309281488175</v>
       </c>
       <c r="O9" t="n">
-        <v>8.63730776248596</v>
+        <v>8.641938024244432</v>
       </c>
       <c r="P9" t="n">
-        <v>257.6978282103938</v>
+        <v>257.6227910757365</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15676,28 +15731,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4272997756901806</v>
+        <v>-0.4259120593793524</v>
       </c>
       <c r="J10" t="n">
+        <v>263</v>
+      </c>
+      <c r="K10" t="n">
         <v>262</v>
       </c>
-      <c r="K10" t="n">
-        <v>261</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.4266390837847207</v>
+        <v>0.4267853599265377</v>
       </c>
       <c r="M10" t="n">
-        <v>2.895065768304104</v>
+        <v>2.89189333744377</v>
       </c>
       <c r="N10" t="n">
-        <v>13.77594022080186</v>
+        <v>13.73674595079138</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71159537406785</v>
+        <v>3.706311637030996</v>
       </c>
       <c r="P10" t="n">
-        <v>243.0645023582884</v>
+        <v>243.0501063871122</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15748,28 +15803,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3359698902085638</v>
+        <v>-0.332429394025914</v>
       </c>
       <c r="J11" t="n">
+        <v>263</v>
+      </c>
+      <c r="K11" t="n">
         <v>262</v>
       </c>
-      <c r="K11" t="n">
-        <v>261</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1377922771809316</v>
+        <v>0.1359831147550911</v>
       </c>
       <c r="M11" t="n">
-        <v>4.241204405794434</v>
+        <v>4.246483994704197</v>
       </c>
       <c r="N11" t="n">
-        <v>39.65301537549249</v>
+        <v>39.58879774222492</v>
       </c>
       <c r="O11" t="n">
-        <v>6.297064028219221</v>
+        <v>6.291962948255888</v>
       </c>
       <c r="P11" t="n">
-        <v>239.9495459309538</v>
+        <v>239.9128173282868</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15820,28 +15875,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9423333110064472</v>
+        <v>-0.9413224002873609</v>
       </c>
       <c r="J12" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09549856692847225</v>
+        <v>0.09601083724836512</v>
       </c>
       <c r="M12" t="n">
-        <v>17.17590779761261</v>
+        <v>17.11506609634272</v>
       </c>
       <c r="N12" t="n">
-        <v>471.2566050032401</v>
+        <v>469.4511693178981</v>
       </c>
       <c r="O12" t="n">
-        <v>21.70844547643244</v>
+        <v>21.66682185549828</v>
       </c>
       <c r="P12" t="n">
-        <v>276.6513552508607</v>
+        <v>276.6408298140308</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15879,7 +15934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33166,7 +33221,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>-46.627399579194694,169.136872459106</t>
+          <t>-46.62735608388586,169.13701845893294</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -33192,6 +33247,73 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:27+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>-46.63023831740059,169.14126268854358</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>-46.62977412649789,169.1404624339151</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>-46.629399523555946,169.1395663541599</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-46.62876458460879,169.13894849017427</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-46.62836480415211,169.13807941325072</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-46.62792049382592,169.1372579252786</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-46.62735608388586,169.13701845893294</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-46.62669044364688,169.13662240233765</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-46.626080544399755,169.1360394260104</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-46.62541270453705,169.1356515360312</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-46.624691014129965,169.13544323777177</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0583/nzd0583.xlsx
+++ b/data/nzd0583/nzd0583.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M264"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12114,7 +12114,7 @@
         <v>217.73</v>
       </c>
       <c r="H263" t="n">
-        <v>246.16</v>
+        <v>233.97</v>
       </c>
       <c r="I263" t="n">
         <v>245.03</v>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>192.08</v>
+        <v>210.21</v>
       </c>
       <c r="C264" t="n">
         <v>197.3</v>
@@ -12159,7 +12159,7 @@
         <v>217.73</v>
       </c>
       <c r="H264" t="n">
-        <v>246.16</v>
+        <v>233.97</v>
       </c>
       <c r="I264" t="n">
         <v>247.71</v>
@@ -12176,6 +12176,137 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>247</v>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="n">
+        <v>206.66</v>
+      </c>
+      <c r="E265" t="n">
+        <v>222.99</v>
+      </c>
+      <c r="F265" t="n">
+        <v>218.49</v>
+      </c>
+      <c r="G265" t="n">
+        <v>218.44</v>
+      </c>
+      <c r="H265" t="n">
+        <v>225</v>
+      </c>
+      <c r="I265" t="n">
+        <v>243.07</v>
+      </c>
+      <c r="J265" t="n">
+        <v>233.43</v>
+      </c>
+      <c r="K265" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="L265" t="n">
+        <v>233.02</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="n">
+        <v>206.66</v>
+      </c>
+      <c r="E266" t="n">
+        <v>228.81</v>
+      </c>
+      <c r="F266" t="n">
+        <v>216.86</v>
+      </c>
+      <c r="G266" t="n">
+        <v>220.43</v>
+      </c>
+      <c r="H266" t="n">
+        <v>228.09</v>
+      </c>
+      <c r="I266" t="n">
+        <v>243.74</v>
+      </c>
+      <c r="J266" t="n">
+        <v>231.86</v>
+      </c>
+      <c r="K266" t="n">
+        <v>238.25</v>
+      </c>
+      <c r="L266" t="n">
+        <v>231.59</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="C267" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="D267" t="n">
+        <v>245.08</v>
+      </c>
+      <c r="E267" t="n">
+        <v>228.81</v>
+      </c>
+      <c r="F267" t="n">
+        <v>216.86</v>
+      </c>
+      <c r="G267" t="n">
+        <v>221.19</v>
+      </c>
+      <c r="H267" t="n">
+        <v>216.07</v>
+      </c>
+      <c r="I267" t="n">
+        <v>230.73</v>
+      </c>
+      <c r="J267" t="n">
+        <v>226.92</v>
+      </c>
+      <c r="K267" t="n">
+        <v>230.83</v>
+      </c>
+      <c r="L267" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14993,6 +15124,36 @@
       </c>
       <c r="B280" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -15155,28 +15316,28 @@
         <v>0.0286</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1910780270716345</v>
+        <v>-0.09495500112424635</v>
       </c>
       <c r="J2" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003373336088892009</v>
+        <v>0.000840152925918547</v>
       </c>
       <c r="M2" t="n">
-        <v>18.61388512281568</v>
+        <v>18.70247032775042</v>
       </c>
       <c r="N2" t="n">
-        <v>566.0646839709801</v>
+        <v>570.4787681615115</v>
       </c>
       <c r="O2" t="n">
-        <v>23.7921139029507</v>
+        <v>23.88469736382505</v>
       </c>
       <c r="P2" t="n">
-        <v>224.4618249062655</v>
+        <v>223.3852807233857</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15227,28 +15388,28 @@
         <v>0.0306</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.250926362903943</v>
+        <v>-4.127019837871566</v>
       </c>
       <c r="J3" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2680276683089654</v>
+        <v>0.2516056378672341</v>
       </c>
       <c r="M3" t="n">
-        <v>38.06413567695475</v>
+        <v>38.23937019559087</v>
       </c>
       <c r="N3" t="n">
-        <v>2525.521098821678</v>
+        <v>2604.400127151262</v>
       </c>
       <c r="O3" t="n">
-        <v>50.25456296518435</v>
+        <v>51.03332369296813</v>
       </c>
       <c r="P3" t="n">
-        <v>308.1428673961782</v>
+        <v>306.7069246693625</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15299,28 +15460,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.698613334328617</v>
+        <v>-1.669586611111457</v>
       </c>
       <c r="J4" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K4" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09642560685179069</v>
+        <v>0.09527654892956749</v>
       </c>
       <c r="M4" t="n">
-        <v>23.55103389065146</v>
+        <v>23.35700472379265</v>
       </c>
       <c r="N4" t="n">
-        <v>1550.919292400599</v>
+        <v>1538.470528553441</v>
       </c>
       <c r="O4" t="n">
-        <v>39.38171266464422</v>
+        <v>39.22334162910449</v>
       </c>
       <c r="P4" t="n">
-        <v>252.001805409406</v>
+        <v>251.6951172315246</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15371,28 +15532,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3364754107873615</v>
+        <v>-0.3003702874512583</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K5" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04765760147001519</v>
+        <v>0.03841418629556503</v>
       </c>
       <c r="M5" t="n">
-        <v>9.337520200195</v>
+        <v>9.401096122017295</v>
       </c>
       <c r="N5" t="n">
-        <v>126.5311680310557</v>
+        <v>128.068241790662</v>
       </c>
       <c r="O5" t="n">
-        <v>11.24860738185202</v>
+        <v>11.31672398667839</v>
       </c>
       <c r="P5" t="n">
-        <v>219.6522633173945</v>
+        <v>219.2687467550579</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15443,28 +15604,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00205527658875659</v>
+        <v>0.00980340243863978</v>
       </c>
       <c r="J6" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K6" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L6" t="n">
-        <v>8.355507083335212e-06</v>
+        <v>0.000192709335777197</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87453531233782</v>
+        <v>3.895158520309558</v>
       </c>
       <c r="N6" t="n">
-        <v>28.5036411708857</v>
+        <v>28.50312686420124</v>
       </c>
       <c r="O6" t="n">
-        <v>5.338880142022829</v>
+        <v>5.338831975647973</v>
       </c>
       <c r="P6" t="n">
-        <v>212.0801005028477</v>
+        <v>211.9549903445051</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15515,28 +15676,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3174912490368344</v>
+        <v>-0.3060110022403483</v>
       </c>
       <c r="J7" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K7" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1158775392752188</v>
+        <v>0.1102811838766407</v>
       </c>
       <c r="M7" t="n">
-        <v>5.05669255644027</v>
+        <v>5.043454386770697</v>
       </c>
       <c r="N7" t="n">
-        <v>43.89855535203931</v>
+        <v>43.70945026255453</v>
       </c>
       <c r="O7" t="n">
-        <v>6.625598490101805</v>
+        <v>6.611312295040563</v>
       </c>
       <c r="P7" t="n">
-        <v>223.3360804425485</v>
+        <v>223.2153970546601</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15587,28 +15748,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7644456403292758</v>
+        <v>-0.7802318016194744</v>
       </c>
       <c r="J8" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K8" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2058767093551377</v>
+        <v>0.2208944961373852</v>
       </c>
       <c r="M8" t="n">
-        <v>9.04161123434522</v>
+        <v>8.889889800595192</v>
       </c>
       <c r="N8" t="n">
-        <v>129.1258984947875</v>
+        <v>124.6730551999629</v>
       </c>
       <c r="O8" t="n">
-        <v>11.36335771217238</v>
+        <v>11.16570889822778</v>
       </c>
       <c r="P8" t="n">
-        <v>242.9136212852171</v>
+        <v>243.0753357810061</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15659,28 +15820,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.742583485839218</v>
+        <v>-0.7393489535651191</v>
       </c>
       <c r="J9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2945272653957833</v>
+        <v>0.2967388845674473</v>
       </c>
       <c r="M9" t="n">
-        <v>6.231701469502525</v>
+        <v>6.22949708158893</v>
       </c>
       <c r="N9" t="n">
-        <v>74.68309281488175</v>
+        <v>74.26267188470979</v>
       </c>
       <c r="O9" t="n">
-        <v>8.641938024244432</v>
+        <v>8.617579235766259</v>
       </c>
       <c r="P9" t="n">
-        <v>257.6227910757365</v>
+        <v>257.5888018111081</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15731,28 +15892,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4259120593793524</v>
+        <v>-0.4278902114841264</v>
       </c>
       <c r="J10" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K10" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4267853599265377</v>
+        <v>0.4335191533841426</v>
       </c>
       <c r="M10" t="n">
-        <v>2.89189333744377</v>
+        <v>2.883664787300541</v>
       </c>
       <c r="N10" t="n">
-        <v>13.73674595079138</v>
+        <v>13.67624720600256</v>
       </c>
       <c r="O10" t="n">
-        <v>3.706311637030996</v>
+        <v>3.698141047337508</v>
       </c>
       <c r="P10" t="n">
-        <v>243.0501063871122</v>
+        <v>243.071047319703</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15803,28 +15964,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.332429394025914</v>
+        <v>-0.320024695098497</v>
       </c>
       <c r="J11" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K11" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1359831147550911</v>
+        <v>0.1285498081130825</v>
       </c>
       <c r="M11" t="n">
-        <v>4.246483994704197</v>
+        <v>4.276358180761194</v>
       </c>
       <c r="N11" t="n">
-        <v>39.58879774222492</v>
+        <v>39.68838443038308</v>
       </c>
       <c r="O11" t="n">
-        <v>6.291962948255888</v>
+        <v>6.299871778884319</v>
       </c>
       <c r="P11" t="n">
-        <v>239.9128173282868</v>
+        <v>239.7820302444335</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15875,28 +16036,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9413224002873609</v>
+        <v>-0.9902335500650224</v>
       </c>
       <c r="J12" t="n">
+        <v>266</v>
+      </c>
+      <c r="K12" t="n">
         <v>263</v>
       </c>
-      <c r="K12" t="n">
-        <v>260</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.09601083724836512</v>
+        <v>0.1064282341484541</v>
       </c>
       <c r="M12" t="n">
-        <v>17.11506609634272</v>
+        <v>17.16468350484553</v>
       </c>
       <c r="N12" t="n">
-        <v>469.4511693178981</v>
+        <v>469.6468182530903</v>
       </c>
       <c r="O12" t="n">
-        <v>21.66682185549828</v>
+        <v>21.6713363282722</v>
       </c>
       <c r="P12" t="n">
-        <v>276.6408298140308</v>
+        <v>277.1589529458118</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15934,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M264"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33221,7 +33382,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>-46.62735608388586,169.13701845893294</t>
+          <t>-46.627399579194694,169.136872459106</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -33258,7 +33419,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>-46.63023831740059,169.14126268854358</t>
+          <t>-46.63010710971014,169.14140303894368</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -33288,7 +33449,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>-46.62735608388586,169.13701845893294</t>
+          <t>-46.627399579194694,169.136872459106</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -33314,6 +33475,199 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-46.629840858093125,169.14168784053368</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-46.62927996946126,169.1396942425641</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-46.62873525569031,169.13897980444168</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-46.628341413629805,169.1381043875161</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-46.62791535278326,169.13726341596742</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-46.62743158505274,169.13676502512757</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-46.626707007288005,169.1365668344581</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-46.62608133011195,169.13603679158805</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-46.625395114332115,169.13571058089812</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-46.624762726885,169.1352027921316</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-46.62976638855154,169.14176749776885</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-46.62927996946126,169.1396942425641</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-46.62869310893119,169.1390248041435</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-46.62835321751645,169.13809178440658</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-46.62790094338042,169.13727880535728</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-46.62742055963524,169.13680203417067</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-46.62670461555708,169.1365748582703</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-46.626086937238085,169.13601799139016</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-46.62540421271794,169.1356800404543</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-46.62476783389878,169.13518566873853</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-46.62976638855154,169.14176749776885</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>-46.62874089564331,169.1415676503754</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>-46.62900192595762,169.13999166604748</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-46.62869310893119,169.1390248041435</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-46.62835321751645,169.13809178440658</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-46.62789544029129,169.13728468271003</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-46.62746344808242,169.13665807010952</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-46.626751057869214,169.136419052482</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-46.626104580021625,169.13595883660295</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-46.6254306871884,169.13559117369513</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-46.624797083108085,169.13508759833678</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0583/nzd0583.xlsx
+++ b/data/nzd0583/nzd0583.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12274,11 +12274,9 @@
       <c r="B267" t="n">
         <v>257.29</v>
       </c>
-      <c r="C267" t="n">
-        <v>340.07</v>
-      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>245.08</v>
+        <v>206.66</v>
       </c>
       <c r="E267" t="n">
         <v>228.81</v>
@@ -12305,6 +12303,141 @@
         <v>223.4</v>
       </c>
       <c r="M267" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="C268" t="n">
+        <v>229.41</v>
+      </c>
+      <c r="D268" t="n">
+        <v>212.03</v>
+      </c>
+      <c r="E268" t="n">
+        <v>221.87</v>
+      </c>
+      <c r="F268" t="n">
+        <v>214.28</v>
+      </c>
+      <c r="G268" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="H268" t="n">
+        <v>214.33</v>
+      </c>
+      <c r="I268" t="n">
+        <v>229.65</v>
+      </c>
+      <c r="J268" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="K268" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="L268" t="n">
+        <v>223.75</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="C269" t="n">
+        <v>229.41</v>
+      </c>
+      <c r="D269" t="n">
+        <v>212.03</v>
+      </c>
+      <c r="E269" t="n">
+        <v>211.21</v>
+      </c>
+      <c r="F269" t="n">
+        <v>249.61</v>
+      </c>
+      <c r="G269" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="H269" t="n">
+        <v>214.33</v>
+      </c>
+      <c r="I269" t="n">
+        <v>229.79</v>
+      </c>
+      <c r="J269" t="n">
+        <v>223.71</v>
+      </c>
+      <c r="K269" t="n">
+        <v>226.67</v>
+      </c>
+      <c r="L269" t="n">
+        <v>219.64</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>278.76</v>
+      </c>
+      <c r="C270" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="D270" t="n">
+        <v>284.09</v>
+      </c>
+      <c r="E270" t="n">
+        <v>206.39</v>
+      </c>
+      <c r="F270" t="n">
+        <v>279.12</v>
+      </c>
+      <c r="G270" t="n">
+        <v>244.93</v>
+      </c>
+      <c r="H270" t="n">
+        <v>243.55</v>
+      </c>
+      <c r="I270" t="n">
+        <v>229.79</v>
+      </c>
+      <c r="J270" t="n">
+        <v>221.16</v>
+      </c>
+      <c r="K270" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="L270" t="n">
+        <v>219.64</v>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12321,7 +12454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15154,6 +15287,36 @@
       </c>
       <c r="B283" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -15316,28 +15479,28 @@
         <v>0.0286</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09495500112424635</v>
+        <v>0.006100940865207741</v>
       </c>
       <c r="J2" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000840152925918547</v>
+        <v>3.419763443202051e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>18.70247032775042</v>
+        <v>19.00739861903742</v>
       </c>
       <c r="N2" t="n">
-        <v>570.4787681615115</v>
+        <v>586.670311169969</v>
       </c>
       <c r="O2" t="n">
-        <v>23.88469736382505</v>
+        <v>24.22127806640205</v>
       </c>
       <c r="P2" t="n">
-        <v>223.3852807233857</v>
+        <v>222.2461331365406</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15388,28 +15551,28 @@
         <v>0.0306</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.127019837871566</v>
+        <v>-4.105003822281523</v>
       </c>
       <c r="J3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2516056378672341</v>
+        <v>0.2553984483837693</v>
       </c>
       <c r="M3" t="n">
-        <v>38.23937019559087</v>
+        <v>37.97326096889326</v>
       </c>
       <c r="N3" t="n">
-        <v>2604.400127151262</v>
+        <v>2548.244469072882</v>
       </c>
       <c r="O3" t="n">
-        <v>51.03332369296813</v>
+        <v>50.48013935274825</v>
       </c>
       <c r="P3" t="n">
-        <v>306.7069246693625</v>
+        <v>306.446560961403</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15460,28 +15623,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.669586611111457</v>
+        <v>-1.633659435302342</v>
       </c>
       <c r="J4" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K4" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09527654892956749</v>
+        <v>0.09265297788141835</v>
       </c>
       <c r="M4" t="n">
-        <v>23.35700472379265</v>
+        <v>23.19474702187828</v>
       </c>
       <c r="N4" t="n">
-        <v>1538.470528553441</v>
+        <v>1538.229165661371</v>
       </c>
       <c r="O4" t="n">
-        <v>39.22334162910449</v>
+        <v>39.22026473216837</v>
       </c>
       <c r="P4" t="n">
-        <v>251.6951172315246</v>
+        <v>251.3129341061002</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15532,28 +15695,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3003702874512583</v>
+        <v>-0.2961262716790332</v>
       </c>
       <c r="J5" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03841418629556503</v>
+        <v>0.03811958895953571</v>
       </c>
       <c r="M5" t="n">
-        <v>9.401096122017295</v>
+        <v>9.351832579153651</v>
       </c>
       <c r="N5" t="n">
-        <v>128.068241790662</v>
+        <v>127.1408677513562</v>
       </c>
       <c r="O5" t="n">
-        <v>11.31672398667839</v>
+        <v>11.27567593323594</v>
       </c>
       <c r="P5" t="n">
-        <v>219.2687467550579</v>
+        <v>219.2236050540885</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15604,28 +15767,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00980340243863978</v>
+        <v>0.08602016571678242</v>
       </c>
       <c r="J6" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K6" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000192709335777197</v>
+        <v>0.008562487920294459</v>
       </c>
       <c r="M6" t="n">
-        <v>3.895158520309558</v>
+        <v>4.345041411066274</v>
       </c>
       <c r="N6" t="n">
-        <v>28.50312686420124</v>
+        <v>49.62582844760609</v>
       </c>
       <c r="O6" t="n">
-        <v>5.338831975647973</v>
+        <v>7.044560202568085</v>
       </c>
       <c r="P6" t="n">
-        <v>211.9549903445051</v>
+        <v>211.1469868023493</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15676,28 +15839,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3060110022403483</v>
+        <v>-0.2805817753125925</v>
       </c>
       <c r="J7" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K7" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1102811838766407</v>
+        <v>0.09006729712953199</v>
       </c>
       <c r="M7" t="n">
-        <v>5.043454386770697</v>
+        <v>5.085490254181369</v>
       </c>
       <c r="N7" t="n">
-        <v>43.70945026255453</v>
+        <v>46.61390068431349</v>
       </c>
       <c r="O7" t="n">
-        <v>6.611312295040563</v>
+        <v>6.827437343858491</v>
       </c>
       <c r="P7" t="n">
-        <v>223.2153970546601</v>
+        <v>222.9468246368982</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15748,28 +15911,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7802318016194744</v>
+        <v>-0.7758992268103005</v>
       </c>
       <c r="J8" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K8" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2208944961373852</v>
+        <v>0.2201115533962277</v>
       </c>
       <c r="M8" t="n">
-        <v>8.889889800595192</v>
+        <v>8.93178099569926</v>
       </c>
       <c r="N8" t="n">
-        <v>124.6730551999629</v>
+        <v>125.4628928488085</v>
       </c>
       <c r="O8" t="n">
-        <v>11.16570889822778</v>
+        <v>11.20102195555426</v>
       </c>
       <c r="P8" t="n">
-        <v>243.0753357810061</v>
+        <v>243.0294894918389</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15820,28 +15983,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7393489535651191</v>
+        <v>-0.7564002735115117</v>
       </c>
       <c r="J9" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K9" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2967388845674473</v>
+        <v>0.3095613900844296</v>
       </c>
       <c r="M9" t="n">
-        <v>6.22949708158893</v>
+        <v>6.251249559471832</v>
       </c>
       <c r="N9" t="n">
-        <v>74.26267188470979</v>
+        <v>74.1125634889315</v>
       </c>
       <c r="O9" t="n">
-        <v>8.617579235766259</v>
+        <v>8.608865400790716</v>
       </c>
       <c r="P9" t="n">
-        <v>257.5888018111081</v>
+        <v>257.7693579369158</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15892,28 +16055,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4278902114841264</v>
+        <v>-0.4439247256242683</v>
       </c>
       <c r="J10" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K10" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4335191533841426</v>
+        <v>0.4456621938318487</v>
       </c>
       <c r="M10" t="n">
-        <v>2.883664787300541</v>
+        <v>2.931854518662424</v>
       </c>
       <c r="N10" t="n">
-        <v>13.67624720600256</v>
+        <v>14.19806695481087</v>
       </c>
       <c r="O10" t="n">
-        <v>3.698141047337508</v>
+        <v>3.768032239088577</v>
       </c>
       <c r="P10" t="n">
-        <v>243.071047319703</v>
+        <v>243.2409809031432</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15964,28 +16127,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.320024695098497</v>
+        <v>-0.3300508635433956</v>
       </c>
       <c r="J11" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K11" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1285498081130825</v>
+        <v>0.1374788092612205</v>
       </c>
       <c r="M11" t="n">
-        <v>4.276358180761194</v>
+        <v>4.267987700743672</v>
       </c>
       <c r="N11" t="n">
-        <v>39.68838443038308</v>
+        <v>39.58563388187604</v>
       </c>
       <c r="O11" t="n">
-        <v>6.299871778884319</v>
+        <v>6.291711522461598</v>
       </c>
       <c r="P11" t="n">
-        <v>239.7820302444335</v>
+        <v>239.8883143497441</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -16036,28 +16199,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9902335500650224</v>
+        <v>-1.053869256025384</v>
       </c>
       <c r="J12" t="n">
+        <v>269</v>
+      </c>
+      <c r="K12" t="n">
         <v>266</v>
       </c>
-      <c r="K12" t="n">
-        <v>263</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1064282341484541</v>
+        <v>0.1193041333662804</v>
       </c>
       <c r="M12" t="n">
-        <v>17.16468350484553</v>
+        <v>17.29439391992303</v>
       </c>
       <c r="N12" t="n">
-        <v>469.6468182530903</v>
+        <v>473.8573447973101</v>
       </c>
       <c r="O12" t="n">
-        <v>21.6713363282722</v>
+        <v>21.76826462530511</v>
       </c>
       <c r="P12" t="n">
-        <v>277.1589529458118</v>
+        <v>277.8357357355132</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -16095,7 +16258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33615,14 +33778,10 @@
           <t>-46.62976638855154,169.14176749776885</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>-46.62874089564331,169.1415676503754</t>
-        </is>
-      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>-46.62900192595762,169.13999166604748</t>
+          <t>-46.62927996946126,169.1396942425641</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -33666,6 +33825,207 @@
         </is>
       </c>
       <c r="M267" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>-46.62976638855154,169.14176749776885</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>-46.629541746502085,169.14071100877118</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-46.629241107108626,169.13973581391372</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-46.62874336640454,169.13897114469705</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-46.62837190096572,169.13807183591507</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-46.627920349007816,169.1372580799459</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-46.627469656544186,169.13663723003594</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-46.626754913178054,169.13640611855416</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-46.626102865744464,169.13596458443814</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-46.625432935017464,169.13558362840044</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-46.624795833143665,169.13509178938168</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-46.62976638855154,169.14176749776885</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>-46.629541746502085,169.14071100877118</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>-46.629241107108626,169.13973581391372</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-46.628820562986675,169.1388887223537</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-46.62811605323408,169.13834500532488</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-46.627920349007816,169.1372580799459</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-46.627469656544186,169.13663723003594</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-46.62675441341588,169.13640779517456</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-46.62611604424244,169.13592039794617</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-46.62544552998671,169.13554135078567</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-46.62481051128717,169.1350425745286</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-46.629611008265584,169.1419337012174</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>-46.62904825359737,169.14123888448827</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-46.628719611757695,169.14029365377428</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-46.628855467985716,169.13885145438672</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-46.62790235137716,169.13857317284464</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-46.62772354099215,169.1374682720401</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-46.62736539667954,169.1369871989397</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-46.62675441341588,169.13640779517456</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-46.62612515132417,169.13588986255346</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-46.62545990892607,169.13549308481714</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-46.62481051128717,169.1350425745286</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
